--- a/QCM3_2_PHY.xlsx
+++ b/QCM3_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79893BE1-B092-40D1-B43F-48FABA42F1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4E7E0C-FA56-434E-A7DE-ADF3631DC4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="163">
   <si>
     <t>Question</t>
   </si>
@@ -63,9 +63,6 @@
     <t>OptionE</t>
   </si>
   <si>
-    <t>À déterminer</t>
-  </si>
-  <si>
     <t>$\tau = 0,5\text{ s}$</t>
   </si>
   <si>
@@ -90,18 +87,6 @@
     <t>$E = 8\text{ V}$</t>
   </si>
   <si>
-    <t>$C = 50\text{ \mu F}$</t>
-  </si>
-  <si>
-    <t>$C = 40\text{ \mu F}$</t>
-  </si>
-  <si>
-    <t>$C = 30\text{ \mu F}$</t>
-  </si>
-  <si>
-    <t>$C = 60\text{ \mu F}$</t>
-  </si>
-  <si>
     <t>$R = 12,5\text{ k}\Omega$</t>
   </si>
   <si>
@@ -120,9 +105,6 @@
     <t>$C = 20\text{ nF}$</t>
   </si>
   <si>
-    <t>$C = 20\text{ \mu F}$</t>
-  </si>
-  <si>
     <t>$C = 10\text{ nF}$</t>
   </si>
   <si>
@@ -147,21 +129,6 @@
     <t>$\frac{du_{AB}}{dt} + \frac{1}{RC} u_{AB} = 0$</t>
   </si>
   <si>
-    <t>$\frac{du_{AB}}{dt} - \frac{1}{RC} u_{AB} = 0$</t>
-  </si>
-  <si>
-    <t>$RC \frac{du_{AB}}{dt} - u_{AB} = 0$</t>
-  </si>
-  <si>
-    <t>$u_{R1}$ : courbe B, $u_{C1}$ : courbe A, $u_{R2}$ : courbe D, $u_{C2}$ : courbe C</t>
-  </si>
-  <si>
-    <t>$u_{R1}$ : courbe B, $u_{C1}$ : courbe C, $u_{R2}$ : courbe D, $u_{C2}$ : courbe A</t>
-  </si>
-  <si>
-    <t>$u_{R1}$ : courbe B, $u_{C1}$ : courbe A, $u_{R2}$ : courbe C, $u_{C2}$ : courbe D</t>
-  </si>
-  <si>
     <t>$6\text{ V}$</t>
   </si>
   <si>
@@ -243,9 +210,6 @@
     <t>$u_{C1} = \frac{Q_T}{C_1 + C_2}$</t>
   </si>
   <si>
-    <t>$u_{C1} = Q_T \frac{C_1 C_2}{C_1 + C_2}$</t>
-  </si>
-  <si>
     <t>La constante de temps $\tau$ :</t>
   </si>
   <si>
@@ -270,263 +234,316 @@
     <t>La valeur de la tension $E$ :</t>
   </si>
   <si>
-    <t>L'énergie $E_{e2}$ emmagasinée par le condensateur $C_2$ :</t>
-  </si>
-  <si>
-    <t>La charge $Q_1$ portée par l'armature positive de $C_1$ :</t>
-  </si>
-  <si>
-    <t>La charge $Q_2$ portée par l'armature positive de $C_2$ :</t>
-  </si>
-  <si>
-    <t>On mesure l'intensité du courant $i(t)$ pour $t &gt; t_1 = 100\text{ ms}$. L'intensité est égale à :</t>
-  </si>
-  <si>
     <t>On a pour $t &gt; t_1$ :</t>
   </si>
   <si>
     <t>L'expression de $u_{C1}$ pour $t &gt; t_1$, en fonction de $Q_T, C_1$ et $C_2$ :</t>
   </si>
   <si>
-    <t>À déterminer (graphique)</t>
+    <t>PHY_QCM2_3_Q1.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM2_3_Q2.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM2_3_Q3.png</t>
+  </si>
+  <si>
+    <t>$\frac{di}{dt} + \frac{1}{RC}i = 0$</t>
+  </si>
+  <si>
+    <t>$RC\frac{di}{dt} + i = E$</t>
+  </si>
+  <si>
+    <t>$\frac{d^2i}{dt^2} + \frac{1}{RC}i = 0$</t>
+  </si>
+  <si>
+    <t>$\frac{di}{dt} + RCi = 0$</t>
+  </si>
+  <si>
+    <t>$R = 4\ \Omega$</t>
+  </si>
+  <si>
+    <t>$R = 400\ \Omega$</t>
+  </si>
+  <si>
+    <t>$R = 300\ \Omega$</t>
+  </si>
+  <si>
+    <t>$R = 500\ \Omega$</t>
+  </si>
+  <si>
+    <t>$U_0 = 0\text{ V}$</t>
+  </si>
+  <si>
+    <t>$U_0 = 8\text{ V}$</t>
+  </si>
+  <si>
+    <t>$U_0 = 4\text{ V}$</t>
+  </si>
+  <si>
+    <t>$U_0 = 2\text{ V}$</t>
+  </si>
+  <si>
+    <t>$U_0 = 12,2\text{ V} ; R = 1\text{ k}\Omega$</t>
+  </si>
+  <si>
+    <t>$U_0 = 12,2\text{ V} ; R = 2\text{ k}\Omega$</t>
+  </si>
+  <si>
+    <t>$U_0 = 2,5\text{ V} ; R = 1\text{ k}\Omega$</t>
+  </si>
+  <si>
+    <t>Les valeurs de $U_0$ et $R$ sont :</t>
+  </si>
+  <si>
+    <t>L'équation différentielle vérifiée par l'intensité de courant $i(t)$ :</t>
+  </si>
+  <si>
+    <t>La résistance R du conducteur ohmique :</t>
+  </si>
+  <si>
+    <t>La valeur de $U_0$ :</t>
+  </si>
+  <si>
+    <t>PHY_QCM2_3_Q4.png</t>
+  </si>
+  <si>
+    <t>PHY_QCM2_3_Q5.png</t>
+  </si>
+  <si>
+    <t>$i(t) = \frac{E-u(t)}{R}$</t>
+  </si>
+  <si>
+    <t>$i(t) = \frac{E+u(t)}{R'}$</t>
+  </si>
+  <si>
+    <t>$i(t) = \frac{E-u(t)}{R'}$</t>
+  </si>
+  <si>
+    <t>$i(t) = \frac{E+u(t)}{R}$</t>
+  </si>
+  <si>
+    <t>$u(t) = \frac{R'E}{R'+R}(1 - e^{-t/\tau})$</t>
+  </si>
+  <si>
+    <t>$u(t) = \frac{R'(R+R')E}{R} e^{-t/\tau}$</t>
+  </si>
+  <si>
+    <t>$u(t) = \frac{RE}{R'+R}(1 - e^{-t/\tau})$</t>
+  </si>
+  <si>
+    <t>$u(t) = E(1 - e^{-t/\tau})$</t>
+  </si>
+  <si>
+    <t>$\dot{u} + \frac{R'+R}{RR'C}u = \frac{E}{RC}$</t>
+  </si>
+  <si>
+    <t>$\dot{u} + \frac{R'R}{R+R'C}u = \frac{E}{RR'}$</t>
+  </si>
+  <si>
+    <t>$\dot{u} + \frac{R'R}{R+R'C}u = \frac{E}{RC}$</t>
+  </si>
+  <si>
+    <t>$\dot{u} + \frac{R'+R}{RR'C}u = E$</t>
+  </si>
+  <si>
+    <t>$i = C\frac{du}{dt} + \frac{u}{R'}$</t>
+  </si>
+  <si>
+    <t>$i = C\frac{du}{dt} + R'u$</t>
+  </si>
+  <si>
+    <t>$i = i_1 - i_2$</t>
+  </si>
+  <si>
+    <t>$8,1 \cdot 10^{-3}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$8,1 \cdot 10^{-4}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$4,5 \cdot 10^{-3}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$1,62 \cdot 10^{-3}\text{ J}$</t>
+  </si>
+  <si>
+    <t>$\tau = RC$</t>
+  </si>
+  <si>
+    <t>$\tau = R'C$</t>
+  </si>
+  <si>
+    <t>$\tau = \left(\frac{R' R}{R' + R}\right) C$</t>
+  </si>
+  <si>
+    <t>$\tau = (R' + R)C$</t>
+  </si>
+  <si>
+    <t>L'expression de la constante de temps est :</t>
+  </si>
+  <si>
+    <t>D'après la loi des nœuds pour l'intensité, on a :</t>
+  </si>
+  <si>
+    <t>L'équation différentielle vérifiée par la tension $u(t)$ aux bornes du condensateur :</t>
+  </si>
+  <si>
+    <t>L'expression de la tension $u(t)$ aux bornes du condensateur :</t>
+  </si>
+  <si>
+    <t>L'expression de la tension $i(t)$ :</t>
+  </si>
+  <si>
+    <t>PHY_QCM2_3_Q6.png</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Dipôle RC :&lt;/b&gt;&lt;/center&gt;
- Les figures (1) et (2) ci-après représentent, respectivement, la variation de $u_R$ en fonction de $du_C/dt$ et la variation de $E_e$, l'énergie emmagasinée dans le condensateur en fonction du temps. On donne : $63^2 = 3969$. En exploitant les courbes (1) et (2), déterminer :</t>
-  </si>
-  <si>
-    <t>PHY_QCM2_3_Q1.png</t>
+ Les figures (1) et (2) ci-après représentent, respectivement, la variation de $u_R$ en fonction de $du_C/dt$ et la variation de $E_e$, l'énergie emmagasinée dans le condensateur en fonction du temps. 
+&lt;br&gt;On donne : $63^2 = 3969$. 
+&lt;br&gt;En exploitant les courbes (1) et (2), déterminer :</t>
+  </si>
+  <si>
+    <t>$C = 50 \mu F$</t>
+  </si>
+  <si>
+    <t>$C = 40 \mu F$</t>
+  </si>
+  <si>
+    <t>$C = 30 \mu F$</t>
+  </si>
+  <si>
+    <t>$C = 60 \mu F$</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Dipôle RC :&lt;/b&gt;&lt;/center&gt;
- On réalise le montage représenté sur le schéma de la figure 1. Données : $e^3 = 20,1 ; e^{0,5} = 1,65 ; e^{-0,5} = 0,61 ; \ln(0,37) \simeq -1$. On place l'interrupteur K en position (1) à un instant de date $t = 0$. Le microampèremètre indique $I_0 = 0,1\text{ \mu A}$. Un système de saisie informatique convenable permet d'obtenir la courbe représentant les variations de la charge $q$ du condensateur en fonction de la tension $u_{AB}$ entre ses bornes (figure 2).</t>
-  </si>
-  <si>
-    <t>PHY_QCM2_3_Q2.png</t>
-  </si>
-  <si>
-    <t>PHY_QCM2_3_Q3.png</t>
-  </si>
-  <si>
-    <t>$\frac{di}{dt} + \frac{1}{RC}i = 0$</t>
-  </si>
-  <si>
-    <t>$RC\frac{di}{dt} + i = E$</t>
-  </si>
-  <si>
-    <t>$\frac{d^2i}{dt^2} + \frac{1}{RC}i = 0$</t>
-  </si>
-  <si>
-    <t>$\frac{di}{dt} + RCi = 0$</t>
-  </si>
-  <si>
-    <t>Option A</t>
-  </si>
-  <si>
-    <t>$R = 4\ \Omega$</t>
-  </si>
-  <si>
-    <t>$R = 400\ \Omega$</t>
-  </si>
-  <si>
-    <t>$R = 300\ \Omega$</t>
-  </si>
-  <si>
-    <t>$R = 500\ \Omega$</t>
-  </si>
-  <si>
-    <t>$U_0 = 0\text{ V}$</t>
-  </si>
-  <si>
-    <t>$U_0 = 8\text{ V}$</t>
-  </si>
-  <si>
-    <t>$U_0 = 4\text{ V}$</t>
-  </si>
-  <si>
-    <t>$U_0 = 2\text{ V}$</t>
-  </si>
-  <si>
-    <t>$\Delta E_c = \frac{1}{2} C(E - U_0)^2$</t>
-  </si>
-  <si>
-    <t>$\Delta E_c = \frac{1}{2} C(E^2 - U_0^2)$</t>
-  </si>
-  <si>
-    <t>$\Delta E_c = \frac{1}{2} C(E + U_0)^2$</t>
-  </si>
-  <si>
-    <t>$\Delta E_c = \frac{1}{2} C U_c^2$</t>
-  </si>
-  <si>
-    <t>Option B</t>
-  </si>
-  <si>
-    <t>$U_0 = 12,2\text{ V} ; R = 1\text{ k}\Omega$</t>
-  </si>
-  <si>
-    <t>$U_0 = 12,2\text{ V} ; R = 2\text{ k}\Omega$</t>
-  </si>
-  <si>
-    <t>$U_0 = 2,5\text{ V} ; R = 1\text{ k}\Omega$</t>
-  </si>
-  <si>
-    <t>$t_1 = 4\text{ ms}$</t>
-  </si>
-  <si>
-    <t>$t_1 = 6\text{ ms}$</t>
-  </si>
-  <si>
-    <t>$t_1 = 10\text{ ms}$</t>
-  </si>
-  <si>
-    <t>$t_1 = 12\text{ ms}$</t>
-  </si>
-  <si>
-    <t>Les valeurs de $U_0$ et $R$ sont :</t>
-  </si>
-  <si>
-    <t>A la date $t_1$, l'énergie emmagasinée par le condensateur est égale à la moitié de sa valeur à $t=0$.</t>
-  </si>
-  <si>
-    <t>L'équation différentielle vérifiée par l'intensité de courant $i(t)$ :</t>
-  </si>
-  <si>
-    <t>La résistance R du conducteur ohmique :</t>
-  </si>
-  <si>
-    <t>La valeur de $U_0$ :</t>
-  </si>
-  <si>
-    <t>L'expression de l'énergie électrique $\Delta E_c$ reçue par le condensateur pendant la durée du régime transitoire :</t>
-  </si>
-  <si>
-    <t>PHY_QCM2_3_Q4.png</t>
+ On réalise le montage représenté sur le schéma de la figure 1. 
+&lt;br&gt;Données : $e^3 = 20,1 ; $\quad$ e^{0,5} = 1,65 ; $\quad$ e^{-0,5} = 0,61 ; $\quad$ \ln(0,37) \simeq -1$. 
+&lt;br&gt;On place l'interrupteur K en position (1) à un instant de date $t = 0$. Le microampèremètre indique $I_0 = 0,1 \mu A$. Un système de saisie informatique convenable permet d'obtenir la courbe représentant les variations de la charge $q$ du condensateur en fonction de la tension $u_{AB}$ entre ses bornes (figure 2).</t>
+  </si>
+  <si>
+    <t>$C = 20 \mu F$</t>
+  </si>
+  <si>
+    <t>Lorsque la tension aux bornes du condensateur prend la valeur $u_{AB} = U_0$, on place l'interrupteur K en position (2) à un instant choisi comme une nouvelle origine des dates ($t = 0$). 
+La courbe de la figure 3 représente les variations de $\ln(u_{AB})$ en fonction du temps ($u_{AB}$ est exprimée en V).
+&lt;br&gt;L'équation différentielle vérifiée par la tension $u_{AB}(t)$ :</t>
+  </si>
+  <si>
+    <t>$\frac{du_{AB}}{dt} + \frac{1}{RC} u_{AB} = U_0$</t>
+  </si>
+  <si>
+    <t>$RC \frac{du_{AB}}{dt} - u_{AB} = U_0$</t>
+  </si>
+  <si>
+    <t>$U_0 = 33,2\text{ V} ; R = 1\text{ k}\Omega$</t>
+  </si>
+  <si>
+    <t>$U_0 = 33,2\text{ V} ; R = 2\text{ k}\Omega$</t>
+  </si>
+  <si>
+    <t>A la date $t_1$, l'énergie emmagasinée par le condensateur est égale à $37%$ de sa valeur à $t=0$. La date t_1 vaut alors :</t>
+  </si>
+  <si>
+    <t>$t_1 = 4 \mu s$</t>
+  </si>
+  <si>
+    <t>$t_1 = 6 \mu s$</t>
+  </si>
+  <si>
+    <t>$t_1 = 8 \mu s$</t>
+  </si>
+  <si>
+    <t>$t_1 = 10 \mu s$</t>
+  </si>
+  <si>
+    <t>$t_1 = 12 \mu s$</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Dipôle RC : &lt;/b&gt;&lt;/center&gt;
-On réalise le montage expérimental représenté sur la figure 1 comportant : un générateur de tension de f.é.m. $E=12\text{ V}$, un conducteur ohmique de résistance $R$, un condensateur de capacité $C=2,5\text{ \mu F}$ dont la tension initiale à ses bornes est $u_C = U_0$ avec $0 &lt; U_0 &lt; E$, un interrupteur K. À un instant choisi comme origine des dates ($t=0$) on place l'interrupteur K en position (1). Un courant d'intensité $i$ circule alors dans le circuit. La courbe de la figure 2 représente l'évolution de $i(t)$ en fonction du temps et la tangente à la courbe à $t=0$.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Deux condensateurs idéaux :&lt;/b&gt;&lt;/center&gt; A l'instant $t = 0$, on ferme l'interrupteur K devant une tension E. On charge les 2 condensateurs idéaux $C_1$ et $C_2$ à l'aide d'un générateur de tension E. On a obtenu les 4 courbes ci-dessous. On donne : $R_1 = 50\ \Omega$, $C_1 = 100\text{ \mu F}$ ; $R_2 = 100\ \Omega$, $C_2 = 10\text{ \mu F}$.</t>
-  </si>
-  <si>
-    <t>PHY_QCM2_3_Q5.png</t>
-  </si>
-  <si>
-    <t>$i(t) = \frac{E-u(t)}{R}$</t>
-  </si>
-  <si>
-    <t>$i(t) = \frac{E+u(t)}{R'}$</t>
-  </si>
-  <si>
-    <t>$i(t) = \frac{E-u(t)}{R'}$</t>
-  </si>
-  <si>
-    <t>$i(t) = \frac{E+u(t)}{R}$</t>
-  </si>
-  <si>
-    <t>$u(t) = \frac{R'E}{R'+R}(1 - e^{-t/\tau})$</t>
-  </si>
-  <si>
-    <t>$u(t) = \frac{R'(R+R')E}{R} e^{-t/\tau}$</t>
-  </si>
-  <si>
-    <t>$u(t) = \frac{RE}{R'+R}(1 - e^{-t/\tau})$</t>
-  </si>
-  <si>
-    <t>$u(t) = E(1 - e^{-t/\tau})$</t>
-  </si>
-  <si>
-    <t>$\dot{u} + \frac{R'+R}{RR'C}u = \frac{E}{RC}$</t>
-  </si>
-  <si>
-    <t>$\dot{u} + \frac{R'R}{R+R'C}u = \frac{E}{RR'}$</t>
-  </si>
-  <si>
-    <t>$\dot{u} + \frac{R'R}{R+R'C}u = \frac{E}{RC}$</t>
-  </si>
-  <si>
-    <t>$\dot{u} + \frac{R'+R}{RR'C}u = E$</t>
-  </si>
-  <si>
-    <t>$i = C\frac{du}{dt} + \frac{u}{R'}$</t>
-  </si>
-  <si>
-    <t>$i = C\frac{du}{dt} + \frac{1}{R'}$</t>
-  </si>
-  <si>
-    <t>$i = C\frac{du}{dt} + R'u$</t>
-  </si>
-  <si>
-    <t>$i = i_1 - i_2$</t>
-  </si>
-  <si>
-    <t>Lorsque la tension aux bornes du condensateur prend la valeur $u_{AB} = U_0$, on place l'interrupteur K en position (2) à un instant choisi comme une nouvelle origine des dates ($t = 0$). La courbe de la figure 3 représente les variations de $\ln(u_{AB})$ en fonction du temps ($u_{AB}$ est exprimée en V).
-L'équation différentielle vérifiée par la tension $u_{AB}(t)$ :</t>
-  </si>
-  <si>
-    <t>A $t_0 = 2\text{ ms}$, calculer :  
+On réalise le montage expérimental représenté sur la figure 1 comportant : 
+&lt;br&gt; * un générateur de tension de f.é.m. $E=12\text{ V}$, 
+&lt;br&gt; * un conducteur ohmique de résistance $R$, 
+&lt;br&gt; * un condensateur de capacité $C=2,5 \mu F$ dont la tension initiale à ses bornes est $u_C = U_0$ avec $0 &lt; U_0 &lt; E$, 
+&lt;br&gt; * un interrupteur K. 
+&lt;br&gt;À un instant choisi comme origine des dates ($t=0$) on place l'interrupteur K en position (1). Un courant d'intensité $i(t)$ circule alors dans le circuit. 
+&lt;br&gt;La courbe de la figure 2 représente l'évolution de $i(t)$ en fonction du temps et la tangente à la courbe à $t=0$.</t>
+  </si>
+  <si>
+    <t>L'expression de l'énergie électrique $E_{él}$ reçue par le condensateur pendant la durée du régime transitoire :</t>
+  </si>
+  <si>
+    <t>$E_{él} = \frac{1}{2} C(E - U_0)^2$</t>
+  </si>
+  <si>
+    <t>$E_{él} = \frac{1}{2} C(E^2 - U_0^2)$</t>
+  </si>
+  <si>
+    <t>$E_{él} = \frac{1}{2} C(E + U_0)^2$</t>
+  </si>
+  <si>
+    <t>$E_{él} = \frac{1}{2} C U_c^2$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Deux condensateurs idéaux :&lt;/b&gt;&lt;/center&gt; 
+&lt;br&gt;A l'instant $t = 0$, on ferme l'interrupteur K durant une durée t_0 = 2 ms. On charge les 2 condensateurs idéaux $C_1$ et $C_2$ (sans résistance de fuite) à l'aide d'un générateur de tension E. On a obtenu les 4 courbes ci-dessous. 
+&lt;br&gt; On donne : $R_1 = 50\ \Omega$, $C_1 = 100 \mu F$ ; $R_2 = 100\ \Omega$, $C_2 = 10 \mu F$.
+&lt;br&gt; e^{\frac {-100}{1.4}} \approx 0 ;$\quad$  e^{\frac {-2}{5}} \approx 0,67; $\quad$ e^{-2} \approx 0,14; ;$\quad$ \frac {100}{11} \approx 9,1</t>
+  </si>
+  <si>
+    <t>$u_{R1}$ : courbe B, &lt;br&gt;$u_{C1}$ : courbe A, &lt;br&gt;$u_{R2}$ : courbe D, &lt;br&gt;$u_{C2}$ : courbe C</t>
+  </si>
+  <si>
+    <t>$u_{R1}$ : courbe B, &lt;br&gt;$u_{C1}$ : courbe C, &lt;br&gt;$u_{R2}$ : courbe D, &lt;br&gt;$u_{C2}$ : courbe A</t>
+  </si>
+  <si>
+    <t>$u_{R1}$ : courbe D, &lt;br&gt;$u_{C1}$ : courbe A, &lt;br&gt;$u_{R2}$ : courbe B, &lt;br&gt;$u_{C2}$ : courbe C</t>
+  </si>
+  <si>
+    <t>$u_{R1}$ : courbe D, &lt;br&gt;$u_{C1}$ : courbe C, &lt;br&gt;$u_{R2}$ : courbe B, &lt;br&gt;$u_{C2}$ : courbe A</t>
+  </si>
+  <si>
+    <t>A $t_0 = 2\text{ ms}$, calculer :  &lt;br&gt;
 l'énergie $E_{e1}$ emmagasinée par le condensateur $C_1$ :</t>
   </si>
   <si>
-    <t>II. A l'instant $t = t_0$, on ouvre l'interrupteur K. On s'intéresse au régime permanent qui s'installe ensuite.
+    <t>A $t_0 = 2\text{ ms}$, calculer :  &lt;br&gt;L'énergie $E_{e2}$ emmagasinée par le condensateur $C_2$ :</t>
+  </si>
+  <si>
+    <t>A $t_0 = 2\text{ ms}$, calculer :  &lt;br&gt;La charge $Q_1$ portée par l'armature positive de $C_1$ :</t>
+  </si>
+  <si>
+    <t>A $t_0 = 2\text{ ms}$, calculer :  &lt;br&gt;La charge $Q_2$ portée par l'armature positive de $C_2$ :</t>
+  </si>
+  <si>
+    <t>II. A l'instant $t = t_0$, on ouvre l'interrupteur K. On s'intéresse au régime permanent qui s'installe ensuite.&lt;br&gt;
 La charge totale $Q_T$ portée par les 2 condensateurs :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Un condensateur réel  :&lt;/b&gt;&lt;/center&gt;</t>
-  </si>
-  <si>
-    <t>$8,1 \cdot 10^{-3}\text{ J}$</t>
-  </si>
-  <si>
-    <t>$8,1 \cdot 10^{-4}\text{ J}$</t>
-  </si>
-  <si>
-    <t>$4,5 \cdot 10^{-3}\text{ J}$</t>
-  </si>
-  <si>
-    <t>$1,62 \cdot 10^{-3}\text{ J}$</t>
-  </si>
-  <si>
-    <t>$\tau = RC$</t>
-  </si>
-  <si>
-    <t>$\tau = R'C$</t>
-  </si>
-  <si>
-    <t>$\tau = \left(\frac{R' R}{R' + R}\right) C$</t>
-  </si>
-  <si>
-    <t>$\tau = (R' + R)C$</t>
-  </si>
-  <si>
-    <t>L'énergie totale $V_{i1}$ emmagasinée par $C_1$ et $C_3$ pour $t=t_j$</t>
-  </si>
-  <si>
-    <t>L'expression de la constante de temps est :</t>
-  </si>
-  <si>
-    <t>D'après la loi des nœuds pour l'intensité, on a :</t>
-  </si>
-  <si>
-    <t>L'équation différentielle vérifiée par la tension $u(t)$ aux bornes du condensateur :</t>
-  </si>
-  <si>
-    <t>L'expression de la tension $u(t)$ aux bornes du condensateur :</t>
-  </si>
-  <si>
-    <t>L'expression de la tension $i(t)$ :</t>
-  </si>
-  <si>
-    <t>PHY_QCM2_3_Q6.png</t>
+    <t>On mesure l'intensité du courant $i(t)$ pour $t &gt; t_1 = 100\text{ ms}$. &lt;br&gt;
+L'intensité est égale à :</t>
+  </si>
+  <si>
+    <t>$u_{C1} = \frac{C_1 + C_2}{Q_T}$</t>
+  </si>
+  <si>
+    <t>L'énergie totale $E_{eT}$ emmagasinée par $C_1$ et $C_3$ pour $t=t_1$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un condensateur réel  :&lt;/b&gt;&lt;/center&gt;
+&lt;br&gt; Un condensateur de capacité C possède une résistance de fuite R^'. Il est associé en série avec un conducteur ohmique de résistance R et un générateur de tension idéal de f.é.m. E
+A l'instant t = 0, le condensateur est déchargé.</t>
+  </si>
+  <si>
+    <t>$i = C\frac{du}{dt} + \frac{u}{R' + R}$</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -547,12 +564,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
       <name val="Consolas"/>
     </font>
     <font>
@@ -664,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -700,26 +711,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1074,789 +1079,793 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14"/>
+      <c r="I2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="16"/>
+      <c r="B3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="G3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>20</v>
-      </c>
       <c r="H3" s="10"/>
-      <c r="I3" s="19" t="s">
-        <v>87</v>
+      <c r="I3" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J3" s="8"/>
       <c r="K3" s="6"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="H4" s="10"/>
-      <c r="I4" s="19" t="s">
-        <v>87</v>
+      <c r="I4" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H5" s="10"/>
-      <c r="I5" s="19" t="s">
-        <v>87</v>
+      <c r="I5" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="16"/>
+      <c r="B7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="G7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="H7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>12</v>
+      <c r="I7" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="14" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="14" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="K8" s="6"/>
     </row>
     <row r="9" spans="1:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="19" t="s">
-        <v>12</v>
+        <v>88</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="216.75" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H12" s="10"/>
-      <c r="I12" s="19" t="s">
-        <v>87</v>
+      <c r="I12" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="H13" s="10"/>
-      <c r="I13" s="19" t="s">
-        <v>87</v>
+      <c r="I13" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
     </row>
     <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="H14" s="10"/>
-      <c r="I14" s="19" t="s">
-        <v>110</v>
+      <c r="I14" s="10" t="s">
+        <v>146</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
     </row>
-    <row r="15" spans="1:11" ht="102" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="153" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>42</v>
+        <v>149</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>43</v>
+        <v>150</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>44</v>
+        <v>152</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="14" t="s">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="K15" s="6"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
+      <c r="A16" s="16"/>
       <c r="B16" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="H16" s="10"/>
-      <c r="I16" s="19" t="s">
-        <v>87</v>
+      <c r="I16" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
     <row r="17" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
+      <c r="A17" s="16"/>
       <c r="B17" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C17" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="19" t="s">
-        <v>12</v>
+      <c r="I17" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H18" s="10"/>
-      <c r="I18" s="19" t="s">
-        <v>12</v>
+      <c r="I18" s="10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="H19" s="10"/>
-      <c r="I19" s="19" t="s">
-        <v>12</v>
+      <c r="I19" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="H20" s="10"/>
-      <c r="I20" s="19" t="s">
-        <v>12</v>
+      <c r="I20" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="14" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
+      <c r="A22" s="16"/>
       <c r="B22" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="H22" s="10"/>
       <c r="I22" s="10" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
+      <c r="A23" s="16"/>
       <c r="B23" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="10" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="10" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="20"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C25" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="H25" s="10"/>
-      <c r="I25" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="I25" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+    </row>
+    <row r="26" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C26" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="H26" s="10"/>
-      <c r="I26" s="19" t="s">
-        <v>12</v>
+      <c r="I26" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="J26" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G27" s="14" t="s">
         <v>162</v>
-      </c>
-      <c r="K26" s="6"/>
-    </row>
-    <row r="27" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>141</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="J27" s="8"/>
       <c r="K27" s="6"/>
     </row>
     <row r="28" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="C28" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="10" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="6"/>
     </row>
     <row r="29" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C29" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="10" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="J29" s="8"/>
       <c r="K29" s="6"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
+      <c r="A30" s="16"/>
       <c r="B30" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C30" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="10" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
